--- a/quizsources/testsheet.xlsx
+++ b/quizsources/testsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hayden.Frobenius\Documents\GitHub\quizbank\quizsources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828B974E-11A6-4846-A7FE-65401844F81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736CCE60-DDB1-4ED9-B2CA-5E34D1B9973E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97A11575-2E20-4433-8B04-0A070EA7B1C7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>Unit</t>
   </si>
@@ -116,37 +116,25 @@
     <t>Correct Row</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Multiple Choice</t>
-  </si>
-  <si>
-    <t>Multiple Answer</t>
-  </si>
-  <si>
-    <t>True False</t>
-  </si>
-  <si>
     <t>stuff</t>
   </si>
   <si>
     <t>Why?</t>
   </si>
   <si>
-    <t>Open Ended</t>
-  </si>
-  <si>
-    <t>FG</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>EF</t>
   </si>
 </sst>
 </file>
@@ -521,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7AEFAC-1CA8-456E-8650-442FDCC593DD}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -533,7 +521,7 @@
     <col min="7" max="10" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -544,10 +532,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -558,11 +546,8 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -573,19 +558,16 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -596,10 +578,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -608,13 +590,10 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -625,22 +604,19 @@
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -651,19 +627,16 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -674,38 +647,41 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Invalid question type." promptTitle="Question Type" sqref="D2:D1048576" xr:uid="{9C64F037-6946-44A4-BD60-9FBA5D19EB93}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Invalid question type." promptTitle="Question Type" sqref="D8:D1048576" xr:uid="{9C64F037-6946-44A4-BD60-9FBA5D19EB93}">
       <formula1>"Multiple Choice,Multiple Answer,True False,Open Ended"</formula1>
     </dataValidation>
   </dataValidations>
